--- a/storageUnits.xlsx
+++ b/storageUnits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henryrussell/henmax/campus-swap/realWebsite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5234EE52-725E-A249-8824-B6EA5DFE1213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0F1BCB-FB28-254A-ABBF-EA546B459152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="11300" windowHeight="17280" xr2:uid="{156C10CA-8258-B94D-99A6-FE3B26E1893E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="9">
   <si>
     <t>Unit #</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>10x15</t>
+  </si>
+  <si>
+    <t>Monthly Rate</t>
   </si>
 </sst>
 </file>
@@ -438,10 +441,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C5C776-1C22-9E47-87B6-50A5CA3F11EF}">
-  <dimension ref="A1:C1048576"/>
+  <dimension ref="A1:D1048576"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -451,8 +454,11 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>214</v>
       </c>
@@ -462,8 +468,11 @@
       <c r="C2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>756</v>
       </c>
@@ -473,8 +482,11 @@
       <c r="C3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>203</v>
       </c>
@@ -484,8 +496,11 @@
       <c r="C4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>204</v>
       </c>
@@ -495,8 +510,11 @@
       <c r="C5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5">
+        <v>198.34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>835</v>
       </c>
@@ -506,8 +524,11 @@
       <c r="C6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>119</v>
       </c>
@@ -517,8 +538,11 @@
       <c r="C7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>121</v>
       </c>
@@ -528,8 +552,11 @@
       <c r="C8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>360</v>
       </c>
@@ -539,8 +566,11 @@
       <c r="C9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D9">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>362</v>
       </c>
@@ -550,8 +580,11 @@
       <c r="C10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D10">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>503</v>
       </c>
@@ -561,8 +594,11 @@
       <c r="C11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D11">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>354</v>
       </c>
@@ -572,8 +608,11 @@
       <c r="C12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D12">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>501</v>
       </c>
@@ -583,8 +622,11 @@
       <c r="C13" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D13">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>506</v>
       </c>
@@ -594,8 +636,11 @@
       <c r="C14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D14">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>515</v>
       </c>
@@ -605,8 +650,11 @@
       <c r="C15" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D15">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>305</v>
       </c>
@@ -616,8 +664,11 @@
       <c r="C16" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>504</v>
       </c>
@@ -627,8 +678,11 @@
       <c r="C17" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>745</v>
       </c>
@@ -638,8 +692,11 @@
       <c r="C18" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>414</v>
       </c>
@@ -649,8 +706,11 @@
       <c r="C19" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>410</v>
       </c>
@@ -660,8 +720,11 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>249</v>
       </c>
@@ -671,8 +734,11 @@
       <c r="C21" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>247</v>
       </c>
@@ -682,8 +748,11 @@
       <c r="C22" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>240</v>
       </c>
@@ -693,8 +762,11 @@
       <c r="C23" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>482</v>
       </c>
@@ -704,8 +776,11 @@
       <c r="C24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D24">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>583</v>
       </c>
@@ -715,8 +790,11 @@
       <c r="C25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>248</v>
       </c>
@@ -726,8 +804,11 @@
       <c r="C26" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D26">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>243</v>
       </c>
@@ -737,8 +818,11 @@
       <c r="C27" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D27">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>580</v>
       </c>
@@ -748,8 +832,11 @@
       <c r="C28" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D28">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>581</v>
       </c>
@@ -758,6 +845,9 @@
       </c>
       <c r="C29" t="s">
         <v>7</v>
+      </c>
+      <c r="D29">
+        <v>115</v>
       </c>
     </row>
     <row r="1048576" spans="2:2" x14ac:dyDescent="0.2">

--- a/storageUnits.xlsx
+++ b/storageUnits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henryrussell/henmax/campus-swap/realWebsite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0F1BCB-FB28-254A-ABBF-EA546B459152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E75C256-AD7F-E347-A892-F125C78D0970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="11300" windowHeight="17280" xr2:uid="{156C10CA-8258-B94D-99A6-FE3B26E1893E}"/>
   </bookViews>
